--- a/output/pdf_financials_xlsx/WOLF.xlsx
+++ b/output/pdf_financials_xlsx/WOLF.xlsx
@@ -669,19 +669,19 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>-0.001188</v>
       </c>
       <c r="C12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.148726</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-0.203891</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>-0.111924</v>
       </c>
     </row>
     <row r="13">
@@ -1045,19 +1045,19 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-1.891125</v>
+        <v>-1.889937</v>
       </c>
       <c r="C27" s="3" t="n">
         <v>1.746418</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>1.098304</v>
+        <v>1.24703</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>1.391721</v>
+        <v>1.595612</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>2.377197</v>
+        <v>2.489121</v>
       </c>
     </row>
     <row r="28">
@@ -1089,19 +1089,19 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.872802</v>
+        <v>-0.871614</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>2.989824</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>2.241314</v>
+        <v>2.39004</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>2.508245</v>
+        <v>2.712136</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>4.291398</v>
+        <v>4.403322</v>
       </c>
     </row>
     <row r="30">
@@ -1111,19 +1111,19 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-6.664931202382754</v>
+        <v>-6.655859341561593</v>
       </c>
       <c r="C30" s="3" t="n">
         <v>13.20863938278536</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>8.820457256763232</v>
+        <v>9.405752902964243</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>9.348837668706649</v>
+        <v>10.10878889400971</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>11.99896255367926</v>
+        <v>12.31190763238275</v>
       </c>
     </row>
     <row r="31">
@@ -8187,7 +8187,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -11007,7 +11007,7 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E192" s="5" t="n">

--- a/output/pdf_financials_xlsx/WOLF.xlsx
+++ b/output/pdf_financials_xlsx/WOLF.xlsx
@@ -2631,19 +2631,19 @@
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>0</v>
+        <v>1.121733</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>1.556515</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>1.453316</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>1.528334</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>2.702454</v>
       </c>
     </row>
     <row r="101">
@@ -5752,7 +5752,11 @@
           <t>Depreciation of property and equipment (note 8)</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr"/>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E59" t="inlineStr">
         <is>
           <t>-</t>
@@ -5787,7 +5791,11 @@
           <t>Depreciation of right-of-use assets (note 10)</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr"/>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E60" t="inlineStr">
         <is>
           <t>-</t>
@@ -5824,7 +5832,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -7046,7 +7054,11 @@
           <t>Depreciation of property and equipment (note 9)</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr"/>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E93" s="5" t="n">
         <v>0.09388000000000001</v>
       </c>
@@ -7085,7 +7097,11 @@
           <t>Depreciation of right-of-use assets (note 11)</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr"/>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E94" s="5" t="n">
         <v>0.120885</v>
       </c>
@@ -7126,7 +7142,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E95" s="5" t="n">

--- a/output/pdf_financials_xlsx/WOLF.xlsx
+++ b/output/pdf_financials_xlsx/WOLF.xlsx
@@ -1744,19 +1744,19 @@
         </is>
       </c>
       <c r="B59" s="3" t="n">
-        <v>25.472586</v>
+        <v>0</v>
       </c>
       <c r="C59" s="3" t="n">
-        <v>24.389253</v>
+        <v>0</v>
       </c>
       <c r="D59" s="3" t="n">
-        <v>23.414253</v>
+        <v>0</v>
       </c>
       <c r="E59" s="3" t="n">
-        <v>42.539198</v>
+        <v>0</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>40.864032</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -1788,19 +1788,19 @@
         </is>
       </c>
       <c r="B61" s="3" t="n">
-        <v>0</v>
+        <v>25.472586</v>
       </c>
       <c r="C61" s="3" t="n">
-        <v>0</v>
+        <v>24.389253</v>
       </c>
       <c r="D61" s="3" t="n">
-        <v>1.778652</v>
+        <v>25.192905</v>
       </c>
       <c r="E61" s="3" t="n">
-        <v>1.251188</v>
+        <v>43.790386</v>
       </c>
       <c r="F61" s="3" t="n">
-        <v>0.676894</v>
+        <v>41.540926</v>
       </c>
     </row>
     <row r="62">
@@ -1854,7 +1854,7 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>0</v>
+        <v>0.006093</v>
       </c>
       <c r="C64" s="3" t="n">
         <v>0</v>
@@ -1920,7 +1920,7 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.013832</v>
       </c>
       <c r="C67" s="3" t="n">
         <v>0</v>
@@ -1986,19 +1986,19 @@
         </is>
       </c>
       <c r="B70" s="3" t="n">
-        <v>0</v>
+        <v>0.135084</v>
       </c>
       <c r="C70" s="3" t="n">
-        <v>0</v>
+        <v>0.181106</v>
       </c>
       <c r="D70" s="3" t="n">
-        <v>0</v>
+        <v>0.07474500000000001</v>
       </c>
       <c r="E70" s="3" t="n">
-        <v>0</v>
+        <v>0.078222</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>0</v>
+        <v>0.165424</v>
       </c>
     </row>
     <row r="71">
@@ -2008,19 +2008,19 @@
         </is>
       </c>
       <c r="B71" s="3" t="n">
-        <v>0</v>
+        <v>0.135084</v>
       </c>
       <c r="C71" s="3" t="n">
-        <v>0</v>
+        <v>0.181106</v>
       </c>
       <c r="D71" s="3" t="n">
-        <v>0</v>
+        <v>0.07474500000000001</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>0</v>
+        <v>0.078222</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>0</v>
+        <v>0.165424</v>
       </c>
     </row>
     <row r="72">
@@ -2096,19 +2096,19 @@
         </is>
       </c>
       <c r="B75" s="3" t="n">
-        <v>17.289664</v>
+        <v>17.15458</v>
       </c>
       <c r="C75" s="3" t="n">
-        <v>1.301488</v>
+        <v>1.120382</v>
       </c>
       <c r="D75" s="3" t="n">
-        <v>1.301679</v>
+        <v>1.226934</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>2.180352</v>
+        <v>2.10213</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>2.525444</v>
+        <v>2.36002</v>
       </c>
     </row>
     <row r="76">
@@ -2206,19 +2206,19 @@
         </is>
       </c>
       <c r="B80" s="3" t="n">
-        <v>0.1934152158628306</v>
+        <v>0.2265545308109471</v>
       </c>
       <c r="C80" s="3" t="n">
-        <v>0.03042649377326746</v>
+        <v>0.03789558693909629</v>
       </c>
       <c r="D80" s="3" t="n">
-        <v>0.02642601777616294</v>
+        <v>0.02940514606198261</v>
       </c>
       <c r="E80" s="3" t="n">
-        <v>0.02257259081588841</v>
+        <v>0.0252856969582321</v>
       </c>
       <c r="F80" s="3" t="n">
-        <v>0.008335176153846935</v>
+        <v>0.01374745739027627</v>
       </c>
     </row>
     <row r="81">
@@ -2785,19 +2785,19 @@
         </is>
       </c>
       <c r="B107" s="3" t="n">
-        <v>0</v>
+        <v>0.180991</v>
       </c>
       <c r="C107" s="3" t="n">
-        <v>0</v>
+        <v>0.211178</v>
       </c>
       <c r="D107" s="3" t="n">
-        <v>0</v>
+        <v>0.232584</v>
       </c>
       <c r="E107" s="3" t="n">
-        <v>0</v>
+        <v>0.085634</v>
       </c>
       <c r="F107" s="3" t="n">
-        <v>0</v>
+        <v>0.07666000000000001</v>
       </c>
     </row>
     <row r="108">
@@ -2851,19 +2851,19 @@
         </is>
       </c>
       <c r="B110" s="3" t="n">
-        <v>0</v>
+        <v>1.380795</v>
       </c>
       <c r="C110" s="3" t="n">
-        <v>0</v>
+        <v>5.523883</v>
       </c>
       <c r="D110" s="3" t="n">
-        <v>0</v>
+        <v>0.125765</v>
       </c>
       <c r="E110" s="3" t="n">
-        <v>0</v>
+        <v>0.239315</v>
       </c>
       <c r="F110" s="3" t="n">
-        <v>0</v>
+        <v>0.090083</v>
       </c>
     </row>
     <row r="111">
@@ -3257,7 +3257,7 @@
         </is>
       </c>
       <c r="B128" s="3" t="n">
-        <v>0</v>
+        <v>-1.454923</v>
       </c>
       <c r="C128" s="3" t="n">
         <v>0</v>
@@ -3782,7 +3782,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>OtherIntangibleAssets</t>
+          <t>GoodwillAndOtherIntangibleAssets</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4043,7 +4043,11 @@
           <t>Lease liabilities (note 10)</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>-</t>
@@ -4883,7 +4887,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>OtherIntangibleAssets</t>
+          <t>GoodwillAndOtherIntangibleAssets</t>
         </is>
       </c>
       <c r="E38" s="5" t="n">
@@ -4963,7 +4967,11 @@
           <t>Lease liabilities (note 11)</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E40" s="5" t="n">
         <v>0.135084</v>
       </c>
@@ -5869,7 +5877,11 @@
           <t>Interest and accretion expense (notes 10 and 11)</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr"/>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E62" t="inlineStr">
         <is>
           <t>-</t>
@@ -5906,7 +5918,11 @@
           <t>Share-based compensation expense (note 16)</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr"/>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E63" t="inlineStr">
         <is>
           <t>-</t>
@@ -6775,7 +6791,11 @@
           <t>Interest and accretion expense (notes 11 and 12)</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr"/>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E86" t="inlineStr">
         <is>
           <t>-</t>
@@ -6855,7 +6875,11 @@
           <t>Share-based compensation expense (note 17)</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr"/>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E88" t="inlineStr">
         <is>
           <t>-</t>
@@ -7265,7 +7289,11 @@
           <t>Interest and accretion expense (notes 12 and 13)</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr"/>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E98" s="5" t="n">
         <v>1.380795</v>
       </c>
@@ -7384,7 +7412,11 @@
           <t>Share-based compensation expense (note 18)</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr"/>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E101" s="5" t="n">
         <v>0.180991</v>
       </c>
@@ -7788,7 +7820,11 @@
           <t>Financing fees paid</t>
         </is>
       </c>
-      <c r="D111" t="inlineStr"/>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>NetOtherFinancingCharges</t>
+        </is>
+      </c>
       <c r="E111" s="5" t="n">
         <v>-1.454923</v>
       </c>
@@ -10236,7 +10272,11 @@
           <t>Income tax recovery (note 19)</t>
         </is>
       </c>
-      <c r="D173" t="inlineStr"/>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E173" s="5" t="n">
         <v>-0.922186</v>
       </c>
